--- a/Limitations and Withdraw Reports.xlsx
+++ b/Limitations and Withdraw Reports.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/tianjiah_msu_edu/Documents/Data Manager/Data-Manager/Follow-up Dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/tianjiah_msu_edu/Documents/Data Manager/followup_dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{095191E4-8009-40D8-8470-7563574A2974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBBC8E57-9214-1140-9F4D-D51343C7380D}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{095191E4-8009-40D8-8470-7563574A2974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{875990A1-CA59-E846-8CCA-95C7584BABA4}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{47C6A4FF-FE40-4202-BED9-35AB477EE46E}"/>
   </bookViews>
@@ -68,7 +68,6 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
-            <scheme val="minor"/>
           </rPr>
           <t>2026 study year 3-20 study,</t>
         </r>
@@ -271,7 +270,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -679,6 +677,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ACC82BF-4E4C-4468-A9CF-1396370CB60F}">
   <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" customWidth="1"/>
+    <col min="4" max="4" width="25.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
